--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_31.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_31.xlsx
@@ -471,103 +471,103 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32803</v>
+        <v>45370</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sophia Azevedo</t>
+          <t>Lívia Moura</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45094</v>
+        <v>45085</v>
       </c>
       <c r="G2" t="n">
-        <v>4995.48</v>
+        <v>8897.610000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70424</v>
+        <v>5418</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mariane Aragão</t>
+          <t>Bruna Novaes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45082</v>
+        <v>45095</v>
       </c>
       <c r="G3" t="n">
-        <v>11530.76</v>
+        <v>11089.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>51228</v>
+        <v>30801</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Augusto das Neves</t>
+          <t>Luana Freitas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45083</v>
+        <v>45099</v>
       </c>
       <c r="G4" t="n">
-        <v>5257.81</v>
+        <v>4065.83</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95361</v>
+        <v>20865</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Luiza Gonçalves</t>
+          <t>Vitor Hugo Viana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,53 +579,53 @@
         <v>4</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45101</v>
+        <v>45097</v>
       </c>
       <c r="G5" t="n">
-        <v>8545.780000000001</v>
+        <v>3199.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95486</v>
+        <v>96237</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ana Moura</t>
+          <t>Luiz Gustavo da Mota</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45082</v>
+        <v>45102</v>
       </c>
       <c r="G6" t="n">
-        <v>4921.9</v>
+        <v>10260.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30985</v>
+        <v>82971</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gabriela Gomes</t>
+          <t>Olivia Fogaça</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -634,80 +634,80 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45104</v>
+        <v>45081</v>
       </c>
       <c r="G7" t="n">
-        <v>7748.34</v>
+        <v>6705.36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>61795</v>
+        <v>78378</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ana Carolina Rocha</t>
+          <t>Mirella Martins</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Operações</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45100</v>
+        <v>45105</v>
       </c>
       <c r="G8" t="n">
-        <v>11243.01</v>
+        <v>2539.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9941</v>
+        <v>5054</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elisa Dias</t>
+          <t>Enrico Dias</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Engenharia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45080</v>
+        <v>45087</v>
       </c>
       <c r="G9" t="n">
-        <v>4044.91</v>
+        <v>7627.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97258</v>
+        <v>43814</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sr. Enrico Vieira</t>
+          <t>Sr. Kevin Pires</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -721,27 +721,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45081</v>
+        <v>45094</v>
       </c>
       <c r="G10" t="n">
-        <v>10156.53</v>
+        <v>11651.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81653</v>
+        <v>50881</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Enzo Gabriel das Neves</t>
+          <t>Srta. Stephany Ramos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45087</v>
+        <v>45098</v>
       </c>
       <c r="G11" t="n">
-        <v>6872.47</v>
+        <v>6562.73</v>
       </c>
     </row>
   </sheetData>
